--- a/public/templates/KIRII_New_Customer_Parts2-4_Questionnaire.xlsx
+++ b/public/templates/KIRII_New_Customer_Parts2-4_Questionnaire.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10719"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0E1741-6C91-454C-BFE4-7581AC7E87B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="660" windowWidth="29360" windowHeight="21680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5200" yWindow="660" windowWidth="29360" windowHeight="21680" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Lists" sheetId="1" state="veryHidden" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
-    <sheet name="Fill In" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Fill In" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="254">
   <si>
     <t>HK District / 香港分區</t>
   </si>
@@ -247,6 +246,9 @@
     <t>Registered Company Name (English) / 公司英文名稱 *</t>
   </si>
   <si>
+    <t>e.g. KIRII (Hong Kong) Limited</t>
+  </si>
+  <si>
     <t>companyNameZh</t>
   </si>
   <si>
@@ -382,6 +384,9 @@
     <t>nar1.directors.0.district</t>
   </si>
   <si>
+    <t>Director 1 / 董事 1 - District / 區</t>
+  </si>
+  <si>
     <t>nar1.directors.0.country</t>
   </si>
   <si>
@@ -424,6 +429,9 @@
     <t>nar1.directors.1.district</t>
   </si>
   <si>
+    <t>Director 2 / 董事 2 - District / 區</t>
+  </si>
+  <si>
     <t>nar1.directors.1.country</t>
   </si>
   <si>
@@ -463,6 +471,9 @@
     <t>nar1.directors.2.district</t>
   </si>
   <si>
+    <t>Director 3 / 董事 3 - District / 區</t>
+  </si>
+  <si>
     <t>nar1.directors.2.country</t>
   </si>
   <si>
@@ -499,69 +510,72 @@
     <t>contacts.0.idNumber</t>
   </si>
   <si>
-    <t>Contact 1 / 聯絡人 1 - ID Number / 身分證號碼</t>
+    <t>Contact 1 / 聯絡人 1 - ID Number / 身分證號碼 *</t>
+  </si>
+  <si>
+    <t>Required. As shown on ID copy / 必須。與身分證副本一致</t>
+  </si>
+  <si>
+    <t>contacts.0.title</t>
+  </si>
+  <si>
+    <t>Contact 1 / 聯絡人 1 - Title / 職位</t>
+  </si>
+  <si>
+    <t>contacts.0.email</t>
+  </si>
+  <si>
+    <t>Contact 1 / 聯絡人 1 - Email / 電郵</t>
+  </si>
+  <si>
+    <t>contacts.0.phoneCountryCode</t>
+  </si>
+  <si>
+    <t>Contact 1 / 聯絡人 1 - Phone Country Code / 電話區號</t>
+  </si>
+  <si>
+    <t>e.g. +852</t>
+  </si>
+  <si>
+    <t>contacts.0.phone</t>
+  </si>
+  <si>
+    <t>Contact 1 / 聯絡人 1 - Phone / 電話</t>
+  </si>
+  <si>
+    <t>contacts.1.nameEnFirst</t>
+  </si>
+  <si>
+    <t>Contact 2 / 聯絡人 2 - Given Name (English) / 英文名 *</t>
+  </si>
+  <si>
+    <t>contacts.1.nameEnMiddle</t>
+  </si>
+  <si>
+    <t>Contact 2 / 聯絡人 2 - Middle Name (English) / 英文中間名</t>
+  </si>
+  <si>
+    <t>contacts.1.nameEnLast</t>
+  </si>
+  <si>
+    <t>Contact 2 / 聯絡人 2 - Surname (English) / 英文姓氏 *</t>
+  </si>
+  <si>
+    <t>contacts.1.nameZh</t>
+  </si>
+  <si>
+    <t>Contact 2 / 聯絡人 2 - Full Name (Chinese) / 中文姓名全名 *</t>
+  </si>
+  <si>
+    <t>contacts.1.idNumber</t>
+  </si>
+  <si>
+    <t>Contact 2 / 聯絡人 2 - ID Number / 身分證號碼</t>
   </si>
   <si>
     <t>As shown on ID copy / 與身分證副本一致</t>
   </si>
   <si>
-    <t>contacts.0.title</t>
-  </si>
-  <si>
-    <t>Contact 1 / 聯絡人 1 - Title / 職位</t>
-  </si>
-  <si>
-    <t>contacts.0.email</t>
-  </si>
-  <si>
-    <t>Contact 1 / 聯絡人 1 - Email / 電郵</t>
-  </si>
-  <si>
-    <t>contacts.0.phoneCountryCode</t>
-  </si>
-  <si>
-    <t>Contact 1 / 聯絡人 1 - Phone Country Code / 電話區號</t>
-  </si>
-  <si>
-    <t>e.g. +852</t>
-  </si>
-  <si>
-    <t>contacts.0.phone</t>
-  </si>
-  <si>
-    <t>Contact 1 / 聯絡人 1 - Phone / 電話</t>
-  </si>
-  <si>
-    <t>contacts.1.nameEnFirst</t>
-  </si>
-  <si>
-    <t>Contact 2 / 聯絡人 2 - Given Name (English) / 英文名 *</t>
-  </si>
-  <si>
-    <t>contacts.1.nameEnMiddle</t>
-  </si>
-  <si>
-    <t>Contact 2 / 聯絡人 2 - Middle Name (English) / 英文中間名</t>
-  </si>
-  <si>
-    <t>contacts.1.nameEnLast</t>
-  </si>
-  <si>
-    <t>Contact 2 / 聯絡人 2 - Surname (English) / 英文姓氏 *</t>
-  </si>
-  <si>
-    <t>contacts.1.nameZh</t>
-  </si>
-  <si>
-    <t>Contact 2 / 聯絡人 2 - Full Name (Chinese) / 中文姓名全名 *</t>
-  </si>
-  <si>
-    <t>contacts.1.idNumber</t>
-  </si>
-  <si>
-    <t>Contact 2 / 聯絡人 2 - ID Number / 身分證號碼</t>
-  </si>
-  <si>
     <t>contacts.1.title</t>
   </si>
   <si>
@@ -631,6 +645,9 @@
     <t>contacts.2.phoneCountryCode</t>
   </si>
   <si>
+    <t>Contact 3 / 聯絡人 3 - Phone Country Code / 電話區號</t>
+  </si>
+  <si>
     <t>contacts.2.phone</t>
   </si>
   <si>
@@ -761,62 +778,35 @@
   </si>
   <si>
     <t>Bank Code / SWIFT Code / 銀行代碼</t>
-  </si>
-  <si>
-    <t>e.g. KIRII (Hong Kong) Limited</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Director 1 / 董事 1 - District / 區</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Director 2 / 董事 2 - District / 區</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Director 3 / 董事 3 - District / 區</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Contact 3 / 聯絡人 3 - Phone Country Code / 電話區號</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="1"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
     <font>
       <b/>
+      <charset val="136"/>
+      <family val="1"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -845,7 +835,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1189,11 +1179,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1207,7 +1197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1221,7 +1211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1235,7 +1225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1246,7 +1236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1254,402 +1244,400 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D90"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -1657,25 +1645,25 @@
     <col min="4" max="4" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C2" t="s">
@@ -1685,7 +1673,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1696,15 +1684,15 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
@@ -1713,40 +1701,40 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -1755,9 +1743,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -1766,43 +1754,43 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>87</v>
       </c>
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -1811,12 +1799,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -1825,12 +1813,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -1839,9 +1827,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
@@ -1850,43 +1838,43 @@
         <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
@@ -1895,12 +1883,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -1909,12 +1897,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
@@ -1923,992 +1911,992 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
         <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
         <v>111</v>
       </c>
-      <c r="B23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
         <v>116</v>
       </c>
-      <c r="B25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>146</v>
+      </c>
+      <c r="B39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>173</v>
+      </c>
+      <c r="B52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B53" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" t="s">
+        <v>180</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>181</v>
+      </c>
+      <c r="B56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57" t="s">
+        <v>184</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>186</v>
+      </c>
+      <c r="B58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>190</v>
+      </c>
+      <c r="B60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>194</v>
+      </c>
+      <c r="B62" t="s">
+        <v>195</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>200</v>
+      </c>
+      <c r="B65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>202</v>
+      </c>
+      <c r="B66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" t="s">
+        <v>205</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s">
+        <v>215</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>218</v>
+      </c>
+      <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>222</v>
+      </c>
+      <c r="B76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>226</v>
+      </c>
+      <c r="B78" t="s">
+        <v>227</v>
+      </c>
+      <c r="C78" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>228</v>
+      </c>
+      <c r="B79" t="s">
+        <v>229</v>
+      </c>
+      <c r="C79" t="s">
+        <v>32</v>
+      </c>
+      <c r="D79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" t="s">
+        <v>231</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>232</v>
+      </c>
+      <c r="B81" t="s">
+        <v>233</v>
+      </c>
+      <c r="C81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" t="s">
+        <v>235</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" t="s">
+        <v>238</v>
+      </c>
+      <c r="C83" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>240</v>
+      </c>
+      <c r="B85" t="s">
+        <v>241</v>
+      </c>
+      <c r="C85" t="s">
+        <v>32</v>
+      </c>
+      <c r="D85" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>242</v>
+      </c>
+      <c r="B86" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" t="s">
+        <v>32</v>
+      </c>
+      <c r="D87" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
         <v>249</v>
       </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>128</v>
-      </c>
-      <c r="B31" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>250</v>
       </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>139</v>
-      </c>
-      <c r="B37" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" t="s">
-        <v>142</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="B89" t="s">
         <v>251</v>
       </c>
-      <c r="C41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>153</v>
-      </c>
-      <c r="B45" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>155</v>
-      </c>
-      <c r="B46" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>159</v>
-      </c>
-      <c r="B48" t="s">
-        <v>160</v>
-      </c>
-      <c r="C48" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>164</v>
-      </c>
-      <c r="B50" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>166</v>
-      </c>
-      <c r="B51" t="s">
-        <v>167</v>
-      </c>
-      <c r="C51" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" t="s">
-        <v>172</v>
-      </c>
-      <c r="C53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>173</v>
-      </c>
-      <c r="B54" t="s">
-        <v>174</v>
-      </c>
-      <c r="C54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>175</v>
-      </c>
-      <c r="B55" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>177</v>
-      </c>
-      <c r="B56" t="s">
-        <v>178</v>
-      </c>
-      <c r="C56" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>179</v>
-      </c>
-      <c r="B57" t="s">
-        <v>180</v>
-      </c>
-      <c r="C57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>181</v>
-      </c>
-      <c r="B58" t="s">
-        <v>182</v>
-      </c>
-      <c r="C58" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>183</v>
-      </c>
-      <c r="B59" t="s">
-        <v>184</v>
-      </c>
-      <c r="C59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>185</v>
-      </c>
-      <c r="B60" t="s">
-        <v>186</v>
-      </c>
-      <c r="C60" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>187</v>
-      </c>
-      <c r="B61" t="s">
-        <v>188</v>
-      </c>
-      <c r="C61" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>189</v>
-      </c>
-      <c r="B62" t="s">
-        <v>190</v>
-      </c>
-      <c r="C62" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>191</v>
-      </c>
-      <c r="B63" t="s">
-        <v>192</v>
-      </c>
-      <c r="C63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" t="s">
-        <v>194</v>
-      </c>
-      <c r="C64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>195</v>
-      </c>
-      <c r="B65" t="s">
-        <v>196</v>
-      </c>
-      <c r="C65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D65" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>197</v>
-      </c>
-      <c r="B66" t="s">
-        <v>198</v>
-      </c>
-      <c r="C66" t="s">
-        <v>32</v>
-      </c>
-      <c r="D66" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" t="s">
-        <v>200</v>
-      </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>201</v>
-      </c>
-      <c r="B68" t="s">
-        <v>202</v>
-      </c>
-      <c r="C68" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>203</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="C89" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>252</v>
       </c>
-      <c r="C69" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>204</v>
-      </c>
-      <c r="B70" t="s">
-        <v>205</v>
-      </c>
-      <c r="C70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>206</v>
-      </c>
-      <c r="B71" t="s">
-        <v>207</v>
-      </c>
-      <c r="C71" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>208</v>
-      </c>
-      <c r="B72" t="s">
-        <v>209</v>
-      </c>
-      <c r="C72" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>210</v>
-      </c>
-      <c r="B73" t="s">
-        <v>211</v>
-      </c>
-      <c r="C73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>212</v>
-      </c>
-      <c r="B74" t="s">
-        <v>213</v>
-      </c>
-      <c r="C74" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>214</v>
-      </c>
-      <c r="B75" t="s">
-        <v>215</v>
-      </c>
-      <c r="C75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>216</v>
-      </c>
-      <c r="B76" t="s">
-        <v>217</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>218</v>
-      </c>
-      <c r="B77" t="s">
-        <v>219</v>
-      </c>
-      <c r="C77" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>220</v>
-      </c>
-      <c r="B78" t="s">
-        <v>221</v>
-      </c>
-      <c r="C78" t="s">
-        <v>32</v>
-      </c>
-      <c r="D78" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>222</v>
-      </c>
-      <c r="B79" t="s">
-        <v>223</v>
-      </c>
-      <c r="C79" t="s">
-        <v>32</v>
-      </c>
-      <c r="D79" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>224</v>
-      </c>
-      <c r="B80" t="s">
-        <v>225</v>
-      </c>
-      <c r="C80" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>226</v>
-      </c>
-      <c r="B81" t="s">
-        <v>227</v>
-      </c>
-      <c r="C81" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>228</v>
-      </c>
-      <c r="B82" t="s">
-        <v>229</v>
-      </c>
-      <c r="C82" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>231</v>
-      </c>
-      <c r="B83" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" t="s">
-        <v>32</v>
-      </c>
-      <c r="D83" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>32</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C84" t="s">
-        <v>32</v>
-      </c>
-      <c r="D84" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>234</v>
-      </c>
-      <c r="B85" t="s">
-        <v>235</v>
-      </c>
-      <c r="C85" t="s">
-        <v>32</v>
-      </c>
-      <c r="D85" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>236</v>
-      </c>
-      <c r="B86" t="s">
-        <v>237</v>
-      </c>
-      <c r="C86" t="s">
-        <v>32</v>
-      </c>
-      <c r="D86" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>238</v>
-      </c>
-      <c r="B87" t="s">
-        <v>239</v>
-      </c>
-      <c r="C87" t="s">
-        <v>32</v>
-      </c>
-      <c r="D87" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>241</v>
-      </c>
-      <c r="B88" t="s">
-        <v>242</v>
-      </c>
-      <c r="C88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D88" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>244</v>
-      </c>
-      <c r="B89" t="s">
-        <v>245</v>
-      </c>
-      <c r="C89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D89" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>246</v>
-      </c>
       <c r="B90" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C90" t="s">
         <v>32</v>
@@ -2918,43 +2906,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C2:C90">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN(TRIM(C2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="custom" showInputMessage="1" promptTitle="Required / 必須" prompt="This field is required. / 此欄必須填寫。" showErrorMessage="1" errorTitle="Required / 必須" error="Contact 1 ID Number is required. / 聯絡人 1 身分證號碼為必須。" sqref="C48">
+      <formula1>LEN(TRIM(C48))&gt;0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid selection / 選項無效" error="Please select a value from the dropdown. / 請從下拉選單選擇。" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>Lists!$A$2:$A$19</xm:f>
-          </x14:formula1>
-          <xm:sqref>C10 C41 C34 C27 C16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid selection / 選項無效" error="Please select a value from the dropdown. / 請從下拉選單選擇。" xr:uid="{00000000-0002-0000-0200-000001000000}">
-          <x14:formula1>
-            <xm:f>Lists!$B$2:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>C14 C8</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid selection / 選項無效" error="Please select a value from the dropdown. / 請從下拉選單選擇。" xr:uid="{00000000-0002-0000-0200-000002000000}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>C15 C9</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid selection / 選項無效" error="Please select a value from the dropdown. / 請從下拉選單選擇。" xr:uid="{00000000-0002-0000-0200-000008000000}">
-          <x14:formula1>
-            <xm:f>Lists!$D$2:$D$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>C82:C83</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>